--- a/child-2.xlsx
+++ b/child-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL-GOCO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL CTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB17483-985F-4079-8864-0633B5DFFE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFCF9806-ABBD-4C8E-B4AB-8D77AD8421A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84790C8E-0792-4CCD-A391-8B2FD57BE431}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13530" xr2:uid="{53CF3A42-671C-47B1-9872-18F98FDBD365}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,17 +97,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>77827</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>506342</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>171899</xdr:rowOff>
+      <xdr:rowOff>95689</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11DA725F-9523-F93E-399A-E0D1F5309B57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5AA5E4-9BA1-385F-502F-60288EED87A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -124,7 +124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="11660227" cy="3219899"/>
+          <a:ext cx="10869542" cy="3143689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -141,17 +141,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>230334</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>95795</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>106236</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>171979</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6DF4B5B-2B0E-AEFA-E50C-31F7FB7DF51D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E105C6BF-A3AA-FA75-1E82-D82F01899A7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -168,7 +168,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="3619500"/>
-          <a:ext cx="12422334" cy="3905795"/>
+          <a:ext cx="10469436" cy="3791479"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -181,21 +181,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>220467</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>133661</xdr:rowOff>
+      <xdr:colOff>439573</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>105268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E0F02C1-AF7E-4214-866B-D1572308B12D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85B46EF3-DD06-EEF5-0E84-7D36A2889B83}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -211,8 +211,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="8001000"/>
-          <a:ext cx="9974067" cy="2229161"/>
+          <a:off x="0" y="7810500"/>
+          <a:ext cx="10193173" cy="3534268"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -540,7 +540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA715C7D-AC54-4EBF-A642-F1AFE7DF86C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E140BB-950E-4766-8A9B-461CC09B2AB9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
